--- a/XLibur.Tests/Resource/Examples/Misc/Formulas.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/Formulas.xlsx
@@ -440,12 +440,13 @@
   <x:dimension ref="A1:G14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="6.139196" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10.282054" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="19.853482" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22.996339" style="0" customWidth="1"/>
-    <x:col min="6" max="7" width="10.282054" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14.853482" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="6.282054" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10.567768" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20.282054" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="23.567768" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10.567768" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="10.424911" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:7">

--- a/XLibur.Tests/Resource/Examples/Misc/Formulas.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/Formulas.xlsx
@@ -481,6 +481,7 @@
       </x:c>
       <x:c r="C2" s="0">
         <x:f>A2+$B$2</x:f>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>7</x:v>
@@ -491,8 +492,9 @@
       <x:c r="F2" s="0">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G2" s="0">
+      <x:c r="G2" s="0" t="str">
         <x:f>IF(C2=F2,"Yes", "No")</x:f>
+        <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7">
@@ -504,6 +506,7 @@
       </x:c>
       <x:c r="C3" s="0">
         <x:f>A3+$B$3</x:f>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>9</x:v>
@@ -514,8 +517,9 @@
       <x:c r="F3" s="0">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G3" s="0">
+      <x:c r="G3" s="0" t="str">
         <x:f>IF(C3=F3,"Yes", "No")</x:f>
+        <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
@@ -525,8 +529,9 @@
       <x:c r="B4" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C4" s="0">
+      <x:c r="C4" s="0" t="str">
         <x:f>"Test" &amp; A4 &amp; "R3C2"</x:f>
+        <x:v>TestAR3C2</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>13</x:v>
@@ -537,8 +542,9 @@
       <x:c r="F4" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="G4" s="0">
+      <x:c r="G4" s="0" t="str">
         <x:f>IF(C4=F4,"Yes", "No")</x:f>
+        <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
@@ -547,11 +553,15 @@
       </x:c>
       <x:c r="B6" s="0">
         <x:f t="array" ref="B6:B6">A2+A3</x:f>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:f t="array" ref="C6:D6">TRANSPOSE(A2:A3)</x:f>
-      </x:c>
-      <x:c r="D6" s="0"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D6" s="0">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="0">

--- a/XLibur.Tests/Resource/Examples/Misc/Formulas.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/Formulas.xlsx
@@ -446,7 +446,7 @@
     <x:col min="4" max="4" width="20.282054" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="23.567768" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="10.567768" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="10.424911" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="10.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:7">
